--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20232.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
     <t>NOYOLA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
     <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
   </si>
 </sst>
 </file>
@@ -661,16 +697,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.77</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -684,16 +723,19 @@
         <v>31</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>31</v>
       </c>
-      <c r="E3">
-        <v>31</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -707,16 +749,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>73.08</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -730,16 +775,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -753,16 +801,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +878,7 @@
         <v>96.77</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -870,16 +921,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>96.15000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -896,16 +947,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -922,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -973,16 +1024,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920132</v>
+        <v>21330051920031</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -996,24 +1047,139 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920235</v>
+        <v>21330051920390</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920390</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920046</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920132</v>
+      </c>
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920235</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920041</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20232.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,58 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
     <t>NOYOLA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
   </si>
 </sst>
 </file>
@@ -525,7 +480,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -534,13 +489,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>96.77</v>
+        <v>96.97</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -551,7 +506,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -560,13 +515,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3">
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -694,7 +649,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -703,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>96.77</v>
+        <v>96.97</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -720,7 +675,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -729,13 +684,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3">
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,19 +818,19 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>8.5</v>
@@ -889,7 +844,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -898,13 +853,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3">
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -921,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>73.08</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -947,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>7.4</v>
@@ -973,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1024,16 +979,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920031</v>
+        <v>20330051920132</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1043,144 +998,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920390</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920390</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920046</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920132</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920235</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920041</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
